--- a/XBRL-template-MPERS/Company/02-SOFP-OrderOfLiquidity.xlsx
+++ b/XBRL-template-MPERS/Company/02-SOFP-OrderOfLiquidity.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -447,355 +447,448 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of financial position [abstract]</t>
+          <t>Disclosure on statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of financial position [abstract]</t>
+          <t>Statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of financial position [table]</t>
+          <t>Assets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
-        </is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'SOFP-Sub-OrdOfLiq'!B26</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>'SOFP-Sub-OrdOfLiq'!C26</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
-        </is>
+          <t>Investment properties</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'SOFP-Sub-OrdOfLiq'!B33</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'SOFP-Sub-OrdOfLiq'!C33</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Biological assets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of financial position [line items]</t>
-        </is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>'SOFP-Sub-OrdOfLiq'!B40</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>'SOFP-Sub-OrdOfLiq'!C40</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Assets [abstract]</t>
-        </is>
+          <t>Investments in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>'SOFP-Sub-OrdOfLiq'!B46</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>'SOFP-Sub-OrdOfLiq'!C46</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
-        </is>
+          <t>Investments in associates</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>'SOFP-Sub-OrdOfLiq'!B53</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>'SOFP-Sub-OrdOfLiq'!C53</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Investment properties</t>
-        </is>
+          <t>Investments in joint ventures</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>'SOFP-Sub-OrdOfLiq'!B60</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'SOFP-Sub-OrdOfLiq'!C60</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Biological assets</t>
+          <t>Other investments</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
-        </is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>'SOFP-Sub-OrdOfLiq'!B67</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>'SOFP-Sub-OrdOfLiq'!C67</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Investments in subsidiaries</t>
-        </is>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>'SOFP-Sub-OrdOfLiq'!B98</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>'SOFP-Sub-OrdOfLiq'!C98</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Investments in associates</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Investments in joint ventures</t>
+          <t>Current tax assets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Other investments</t>
+          <t>Derivative financial assets</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inventories</t>
-        </is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>'SOFP-Sub-OrdOfLiq'!B114</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>'SOFP-Sub-OrdOfLiq'!C114</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trade and other receivables</t>
+          <t>Other assets</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Deferred tax assets</t>
-        </is>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>*Total assets</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>1*B6+1*B7+1*B10+1*B11+1*B12+1*B16+1*B14+1*B19+1*B8+1*B15+1*B17+1*B18+1*B20+1*B9+1*B13</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>1*C6+1*C7+1*C10+1*C11+1*C12+1*C16+1*C14+1*C19+1*C8+1*C15+1*C17+1*C18+1*C20+1*C9+1*C13</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Current tax assets</t>
+          <t>Equity and liabilities</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Derivative financial assets</t>
+          <t>Equity</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
-        </is>
+          <t>Issued capital</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>'SOFP-Sub-OrdOfLiq'!B119</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>'SOFP-Sub-OrdOfLiq'!C119</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Other assets</t>
+          <t>Retained earnings</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>*Total assets</t>
-        </is>
-      </c>
-      <c r="B26">
-        <f>1*B11+1*B12+1*B15+1*B16+1*B17+1*B21+1*B19+1*B24+1*B13+1*B20+1*B22+1*B23+1*B25+1*B14+1*B18</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>1*C11+1*C12+1*C15+1*C16+1*C17+1*C21+1*C19+1*C24+1*C13+1*C20+1*C22+1*C23+1*C25+1*C14+1*C18</f>
-        <v/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equity and liabilities [abstract]</t>
-        </is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>'SOFP-Sub-OrdOfLiq'!B130</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>'SOFP-Sub-OrdOfLiq'!C130</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Equity [abstract]</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity attributable to owners</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B24+1*B25+-1*B26+1*B27</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C24+1*C25+-1*C26+1*C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Issued capital</t>
-        </is>
+          <t>Equity - other components</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>'SOFP-Sub-OrdOfLiq'!B136</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>'SOFP-Sub-OrdOfLiq'!C136</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Retained earnings</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Treasury shares</t>
-        </is>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>1*B24+1*B25+-1*B26+1*B27+1*B29+1*B30</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>1*C24+1*C25+-1*C26+1*C27+1*C29+1*C30</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Reserves</t>
+          <t>Liabilities</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity attributable to owners</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Loans and borrowings</t>
         </is>
       </c>
       <c r="B33">
-        <f>1*B29+1*B30+-1*B31+1*B32</f>
+        <f>'SOFP-Sub-OrdOfLiq'!B154</f>
         <v/>
       </c>
       <c r="C33">
-        <f>1*C29+1*C30+-1*C31+1*C32</f>
+        <f>'SOFP-Sub-OrdOfLiq'!C154</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Equity - other components</t>
-        </is>
+          <t>Employee benefits</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>'SOFP-Sub-OrdOfLiq'!B162</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>'SOFP-Sub-OrdOfLiq'!C162</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
-        </is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>'SOFP-Sub-OrdOfLiq'!B170</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>'SOFP-Sub-OrdOfLiq'!C170</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity</t>
-        </is>
-      </c>
-      <c r="B36">
-        <f>1*B29+1*B30+-1*B31+1*B32+1*B34+1*B35</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>1*C29+1*C30+-1*C31+1*C32+1*C34+1*C35</f>
-        <v/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Deferred tax liabilities</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liabilities [abstract]</t>
-        </is>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>'SOFP-Sub-OrdOfLiq'!B196</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>'SOFP-Sub-OrdOfLiq'!C196</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Loans and borrowings</t>
+          <t>Current tax liabilities</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Employee benefits</t>
+          <t>Derivative financial liabilities</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Provisions</t>
+          <t>Other liabilities</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Deferred tax liabilities</t>
-        </is>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>*Total liabilities</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>1*B33+1*B34+1*B35+1*B37+1*B38+1*B39+1*B40+1*B36</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>1*C33+1*C34+1*C35+1*C37+1*C38+1*C39+1*C40+1*C36</f>
+        <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Trade and other payables</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Current tax liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Derivative financial liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Other liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>*Total liabilities</t>
-        </is>
-      </c>
-      <c r="B46">
-        <f>1*B38+1*B39+1*B40+1*B42+1*B43+1*B44+1*B45+1*B41</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>1*C38+1*C39+1*C40+1*C42+1*C43+1*C44+1*C45+1*C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>*Total equity and liabilities</t>
         </is>
       </c>
-      <c r="B47">
-        <f>1*B36+1*B46</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>1*C36+1*C46</f>
+      <c r="B42">
+        <f>1*B31+1*B41</f>
+        <v/>
+      </c>
+      <c r="C42">
+        <f>1*C31+1*C41</f>
         <v/>
       </c>
     </row>
@@ -810,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -839,1657 +932,1622 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Disclosure on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Statement on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [table]</t>
+          <t>Sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Land and buildings</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Land</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement on sub-classification of assets, liabilities and equity [line items]</t>
+          <t>Freehold land</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sub-classification of assets, liabilities and equity [abstract]</t>
+          <t>Long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Property, plant and equipment [abstract]</t>
+          <t>Short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Land and buildings [abstract]</t>
-        </is>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>*Total land</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>1*B9+1*B10+1*B11</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>1*C9+1*C10+1*C11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Land [abstract]</t>
+          <t>Buildings</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Freehold land</t>
+          <t>Building on freehold land</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Long term leasehold land</t>
+          <t>Building on long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Short term leasehold land</t>
+          <t>Building on short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>*Total land</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>1*B14+1*B15+1*B16</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>1*C14+1*C15+1*C16</f>
-        <v/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Leased properties</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Buildings [abstract]</t>
-        </is>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>*Total buildings</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>1*B14+1*B15+1*B16+1*B17</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>1*C14+1*C15+1*C16+1*C17</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Building on freehold land</t>
-        </is>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>*Total land and buildings</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>1*B12+1*B18</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>1*C12+1*C18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Building on long term leasehold land</t>
+          <t>Machinery</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Building on short term leasehold land</t>
+          <t>Vehicles</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Leased properties</t>
+          <t>Office equipment, fixture and fittings</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>*Total buildings</t>
-        </is>
-      </c>
-      <c r="B23">
-        <f>1*B19+1*B20+1*B21+1*B22</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>1*C19+1*C20+1*C21+1*C22</f>
-        <v/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Plant and equipment</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>*Total land and buildings</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>1*B17+1*B23</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>1*C17+1*C23</f>
-        <v/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Construction in progress/Asset work-in progress</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Other property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Vehicles</t>
-        </is>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>*Total property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B25</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Office equipment, fixture and fittings</t>
+          <t>Investment properties</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant and equipment</t>
+          <t>Freehold land</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Construction in progress/Asset work-in progress</t>
+          <t>Long term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other property, plant and equipment</t>
+          <t>Short term leasehold land</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>*Total property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B31">
-        <f>1*B24+1*B25+1*B26+1*B27+1*B28+1*B29+1*B30</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>1*C24+1*C25+1*C26+1*C27+1*C28+1*C29+1*C30</f>
-        <v/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Investment properties [abstract]</t>
+          <t>Other investment property</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Freehold land</t>
-        </is>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>*Total investment properties</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>1*B28+1*B29+1*B30+1*B31+1*B32</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>1*C28+1*C29+1*C30+1*C31+1*C32</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Long term leasehold land</t>
+          <t>Intangible assets and goodwill</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Short term leasehold land</t>
+          <t>Intangible assets other than goodwill</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Copyrights, patents and other industrial property rights, service and operating rights</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Other investment property</t>
+          <t>Other intangible assets</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>*Total investment properties</t>
+          <t>*Total intangible assets other than goodwill</t>
         </is>
       </c>
       <c r="B38">
-        <f>1*B33+1*B34+1*B35+1*B36+1*B37</f>
+        <f>1*B36+1*B37</f>
         <v/>
       </c>
       <c r="C38">
-        <f>1*C33+1*C34+1*C35+1*C36+1*C37</f>
+        <f>1*C36+1*C37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intangible assets and goodwill [abstract]</t>
+          <t>Goodwill</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Intangible assets other than goodwill [abstract]</t>
-        </is>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>*Total intangible assets and goodwill</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>1*B39+1*B38</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>1*C39+1*C38</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Copyrights, patents and other industrial property rights, service and operating rights</t>
+          <t>Investments in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Other intangible assets</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>*Total intangible assets other than goodwill</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>1*B41+1*B42</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>1*C41+1*C42</f>
-        <v/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Quoted shares in Malaysia</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>*Total intangible assets and goodwill</t>
-        </is>
-      </c>
-      <c r="B45">
-        <f>1*B44+1*B43</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>1*C44+1*C43</f>
-        <v/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other investments in subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Investments in subsidiaries [abstract]</t>
-        </is>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>*Total investments in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B46">
+        <f>1*B42+1*B43+1*B44+1*B45</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>1*C42+1*C43+1*C44+1*C45</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unquoted shares, net of impairment losses</t>
+          <t>Investments in associates</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Quoted shares in Malaysia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Other investments in subsidiaries</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>*Total investments in subsidiaries</t>
-        </is>
-      </c>
-      <c r="B51">
-        <f>1*B47+1*B48+1*B49+1*B50</f>
-        <v/>
-      </c>
-      <c r="C51">
-        <f>1*C47+1*C48+1*C49+1*C50</f>
-        <v/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of post-acquisition profits and reserves</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Investments in associates [abstract]</t>
+          <t>Other investments in associates</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unquoted shares, net of impairment losses</t>
-        </is>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>*Total investments in associates</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>1*B48+1*B49+1*B50+1*B51+1*B52</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>1*C48+1*C49+1*C50+1*C51+1*C52</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Investments in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Unquoted shares, net of impairment losses</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Share of post-acquisition profits and reserves</t>
+          <t>Quoted shares in Malaysia</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Other investments in associates</t>
+          <t>Quoted shares outside Malaysia</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>*Total investments in associates</t>
-        </is>
-      </c>
-      <c r="B58">
-        <f>1*B53+1*B54+1*B55+1*B56+1*B57</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>1*C53+1*C54+1*C55+1*C56+1*C57</f>
-        <v/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of post-acquisition profits and reserves</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Investments in joint ventures [abstract]</t>
+          <t>Other investments in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unquoted shares, net of impairment losses</t>
-        </is>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>*Total of investments in joint ventures</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>1*B55+1*B56+1*B57+1*B58+1*B59</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>1*C55+1*C56+1*C57+1*C58+1*C59</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Quoted shares in Malaysia</t>
+          <t>Inventories</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Quoted shares outside Malaysia</t>
+          <t>Raw materials</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Share of post-acquisition profits and reserves</t>
+          <t>Work in progress</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Other investments in joint ventures</t>
+          <t>Finished goods</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>*Total of investments in joint ventures</t>
-        </is>
-      </c>
-      <c r="B65">
-        <f>1*B60+1*B61+1*B62+1*B63+1*B64</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>1*C60+1*C61+1*C62+1*C63+1*C64</f>
-        <v/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Spare parts</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Inventories [abstract]</t>
+          <t>Other inventories</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Raw materials</t>
-        </is>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>*Total inventories</t>
+        </is>
+      </c>
+      <c r="B67">
+        <f>1*B62+1*B63+1*B64+1*B65+1*B66</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>1*C62+1*C63+1*C64+1*C65+1*C66</f>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Work in progress</t>
+          <t>Trade and other receivables</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Finished goods</t>
+          <t>Trade receivables</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Spare parts</t>
+          <t>Trade receivables due from contract customers</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Other inventories</t>
+          <t>Trade receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>*Total inventories</t>
-        </is>
-      </c>
-      <c r="B72">
-        <f>1*B67+1*B68+1*B69+1*B70+1*B71</f>
-        <v/>
-      </c>
-      <c r="C72">
-        <f>1*C67+1*C68+1*C69+1*C70+1*C71</f>
-        <v/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Trade receivables due from subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Trade and other receivables [abstract]</t>
+          <t>Trade receivables from associates</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Trade receivables [abstract]</t>
+          <t>Trade receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Trade receivables due from contract customers</t>
+          <t>Trade receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Trade receivables due from holding company</t>
+          <t>Other trade receivables</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Trade receivables due from subsidiaries</t>
-        </is>
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade receivables</t>
+        </is>
+      </c>
+      <c r="B77">
+        <f>1*B70+1*B71+1*B72+1*B73+1*B74+1*B75+1*B76</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>1*C70+1*C71+1*C72+1*C73+1*C74+1*C75+1*C76</f>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Trade receivables from associates</t>
+          <t>Other receivables</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Trade receivables due from joint ventures</t>
+          <t>Other receivables due from related parties</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Trade receivables due from other related parties</t>
+          <t>Other receivables due from holding company</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Other trade receivables</t>
+          <t>Other receivables due from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>*Total trade receivables</t>
-        </is>
-      </c>
-      <c r="B82">
-        <f>1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B81</f>
-        <v/>
-      </c>
-      <c r="C82">
-        <f>1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C81</f>
-        <v/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Other receivables due from associates</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Other receivables [abstract]</t>
+          <t>Other receivables due from joint ventures</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Other receivables due from related parties [abstract]</t>
+          <t>Other receivables due from other related parties</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Other receivables due from holding company</t>
-        </is>
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>*Total other receivables due from related parties</t>
+        </is>
+      </c>
+      <c r="B85">
+        <f>1*B80+1*B81+1*B82+1*B83+1*B84</f>
+        <v/>
+      </c>
+      <c r="C85">
+        <f>1*C80+1*C81+1*C82+1*C83+1*C84</f>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Other receivables due from subsidiaries</t>
+          <t>Prepayments and accrued income</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Other receivables due from associates</t>
+          <t>Prepayments</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Other receivables due from joint ventures</t>
+          <t>Accrued income</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Other receivables due from other related parties</t>
-        </is>
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>*Total prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B89">
+        <f>1*B87+1*B88</f>
+        <v/>
+      </c>
+      <c r="C89">
+        <f>1*C87+1*C88</f>
+        <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>*Total other receivables due from related parties</t>
-        </is>
-      </c>
-      <c r="B90">
-        <f>1*B85+1*B86+1*B87+1*B88+1*B89</f>
-        <v/>
-      </c>
-      <c r="C90">
-        <f>1*C85+1*C86+1*C87+1*C88+1*C89</f>
-        <v/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Non-trade receivables</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Prepayments and accrued income [abstract]</t>
+          <t>Interest receivables</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Prepayments</t>
+          <t>Deposits</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Accrued income</t>
+          <t>Dividends receivables</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>*Total prepayments and accrued income</t>
-        </is>
-      </c>
-      <c r="B94">
-        <f>1*B92+1*B93</f>
-        <v/>
-      </c>
-      <c r="C94">
-        <f>1*C92+1*C93</f>
-        <v/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Lease and hire purchase receivables</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Non-trade receivables [abstract]</t>
+          <t>Other non-trade receivables</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Interest receivables</t>
-        </is>
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-trade receivables</t>
+        </is>
+      </c>
+      <c r="B96">
+        <f>1*B91+1*B92+1*B93+1*B94+1*B95</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>1*C91+1*C92+1*C93+1*C94+1*C95</f>
+        <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Deposits</t>
-        </is>
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>*Total other receivables</t>
+        </is>
+      </c>
+      <c r="B97">
+        <f>1*B85+1*B89+1*B96</f>
+        <v/>
+      </c>
+      <c r="C97">
+        <f>1*C85+1*C89+1*C96</f>
+        <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Dividends receivables</t>
-        </is>
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade and other receivables</t>
+        </is>
+      </c>
+      <c r="B98">
+        <f>1*B77+1*B97</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>1*C77+1*C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lease and hire purchase receivables</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Other non-trade receivables</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-trade receivables</t>
-        </is>
-      </c>
-      <c r="B101">
-        <f>1*B96+1*B97+1*B98+1*B99+1*B100</f>
-        <v/>
-      </c>
-      <c r="C101">
-        <f>1*C96+1*C97+1*C98+1*C99+1*C100</f>
-        <v/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cash in hand</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>*Total other receivables</t>
-        </is>
-      </c>
-      <c r="B102">
-        <f>1*B90+1*B94+1*B101</f>
-        <v/>
-      </c>
-      <c r="C102">
-        <f>1*C90+1*C94+1*C101</f>
-        <v/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Balances with banks</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>*Total trade and other receivables</t>
+          <t>*Total cash</t>
         </is>
       </c>
       <c r="B103">
-        <f>1*B82+1*B102</f>
+        <f>1*B101+1*B102</f>
         <v/>
       </c>
       <c r="C103">
-        <f>1*C82+1*C102</f>
+        <f>1*C101+1*C102</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents [abstract]</t>
+          <t>Cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cash [abstract]</t>
+          <t>Deposits placed with licensed banks</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cash in hand</t>
+          <t>Deposit placed with other corporations</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Balances with banks</t>
+          <t>Fixed deposits with financial institutions</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
-        <is>
-          <t>*Total cash</t>
-        </is>
-      </c>
-      <c r="B108">
-        <f>1*B106+1*B107</f>
-        <v/>
-      </c>
-      <c r="C108">
-        <f>1*C106+1*C107</f>
-        <v/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cash equivalents with other financial institutions</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cash equivalents [abstract]</t>
+          <t>Short-term deposits</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Deposits placed with licensed banks</t>
+          <t>Short-term investments</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Deposit placed with other corporations</t>
+          <t>Other banking arrangements</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Fixed deposits with financial institutions</t>
-        </is>
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>*Total cash equivalents</t>
+        </is>
+      </c>
+      <c r="B112">
+        <f>1*B105+1*B106+1*B107+1*B108+1*B109+1*B110+1*B111</f>
+        <v/>
+      </c>
+      <c r="C112">
+        <f>1*C105+1*C106+1*C107+1*C108+1*C109+1*C110+1*C111</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cash equivalents with other financial institutions</t>
+          <t>Other cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Short-term deposits</t>
-        </is>
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>*Total cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B114">
+        <f>1*B103+1*B112+1*B113</f>
+        <v/>
+      </c>
+      <c r="C114">
+        <f>1*C103+1*C112+1*C113</f>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Short-term investments</t>
+          <t>Issued capital</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Other banking arrangements</t>
+          <t>Capital from ordinary shares</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr">
-        <is>
-          <t>*Total cash equivalents</t>
-        </is>
-      </c>
-      <c r="B117">
-        <f>1*B110+1*B111+1*B112+1*B113+1*B114+1*B115+1*B116</f>
-        <v/>
-      </c>
-      <c r="C117">
-        <f>1*C110+1*C111+1*C112+1*C113+1*C114+1*C115+1*C116</f>
-        <v/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Capital from redeemable preference shares</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Other cash and cash equivalents</t>
+          <t>Capital from non-redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>*Total cash and cash equivalents</t>
+          <t>*Total issued capital</t>
         </is>
       </c>
       <c r="B119">
-        <f>1*B108+1*B117+1*B118</f>
+        <f>1*B116+1*B117+1*B118</f>
         <v/>
       </c>
       <c r="C119">
-        <f>1*C108+1*C117+1*C118</f>
+        <f>1*C116+1*C117+1*C118</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Issued capital [abstract]</t>
+          <t>Reserves</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Capital from ordinary shares</t>
+          <t>Non-distributable</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Capital from redeemable preference shares</t>
+          <t>Capital reserve</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Capital from non-redeemable preference shares</t>
+          <t>Foreign currency translation reserve</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr">
-        <is>
-          <t>*Total issued capital</t>
-        </is>
-      </c>
-      <c r="B124">
-        <f>1*B121+1*B122+1*B123</f>
-        <v/>
-      </c>
-      <c r="C124">
-        <f>1*C121+1*C122+1*C123</f>
-        <v/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Revaluation surplus</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Reserves [abstract]</t>
+          <t>Other non-distributable reserves</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Non-distributable [abstract]</t>
-        </is>
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-distributable reserves</t>
+        </is>
+      </c>
+      <c r="B126">
+        <f>1*B122+1*B123+1*B124+1*B125</f>
+        <v/>
+      </c>
+      <c r="C126">
+        <f>1*C122+1*C123+1*C124+1*C125</f>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Capital reserve</t>
+          <t>Distributable</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve</t>
+          <t>Other distributable reserves</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Revaluation surplus</t>
-        </is>
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>*Total distributable reserves</t>
+        </is>
+      </c>
+      <c r="B129">
+        <f>1*B128</f>
+        <v/>
+      </c>
+      <c r="C129">
+        <f>1*C128</f>
+        <v/>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Other non-distributable reserves</t>
-        </is>
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>*Total reserves</t>
+        </is>
+      </c>
+      <c r="B130">
+        <f>1*B126+1*B129</f>
+        <v/>
+      </c>
+      <c r="C130">
+        <f>1*C126+1*C129</f>
+        <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-distributable reserves</t>
-        </is>
-      </c>
-      <c r="B131">
-        <f>1*B127+1*B128+1*B129+1*B130</f>
-        <v/>
-      </c>
-      <c r="C131">
-        <f>1*C127+1*C128+1*C129+1*C130</f>
-        <v/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Equity - others components</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Distributable [abstract]</t>
+          <t>Perpetual Sukuk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Other distributable reserves</t>
+          <t>Equity component of Irredeemable Convertible Unsecured Loan Stocks (ICULS)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>*Total distributable reserves</t>
-        </is>
-      </c>
-      <c r="B134">
-        <f>1*B133</f>
-        <v/>
-      </c>
-      <c r="C134">
-        <f>1*C133</f>
-        <v/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Equity component of preference shares</t>
+        </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>*Total reserves</t>
-        </is>
-      </c>
-      <c r="B135">
-        <f>1*B131+1*B134</f>
-        <v/>
-      </c>
-      <c r="C135">
-        <f>1*C131+1*C134</f>
-        <v/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Equity components of other financial instruments</t>
+        </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Equity - others components [abstract]</t>
-        </is>
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>*Total equity - other components</t>
+        </is>
+      </c>
+      <c r="B136">
+        <f>1*B132+1*B133+1*B134+1*B135</f>
+        <v/>
+      </c>
+      <c r="C136">
+        <f>1*C132+1*C133+1*C134+1*C135</f>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Perpetual Sukuk</t>
+          <t>Loans and Borrowings</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Equity component of Irredeemable Convertible Unsecured Loan Stocks (ICULS)</t>
+          <t>Secured bank loans</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Equity component of preference shares</t>
+          <t>Unsecured bank loans</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Equity components of other financial instruments</t>
+          <t>Secured convertible notes</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>*Total equity - other components</t>
-        </is>
-      </c>
-      <c r="B141">
-        <f>1*B137+1*B138+1*B139+1*B140</f>
-        <v/>
-      </c>
-      <c r="C141">
-        <f>1*C137+1*C138+1*C139+1*C140</f>
-        <v/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Unsecured convertible notes</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Loans and Borrowings [abstract]</t>
+          <t>Bank overdrafts</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Secured bank loans</t>
+          <t>Unsecured bank overdrafts</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Unsecured bank loans</t>
+          <t>Redeemable preference shares</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Secured convertible notes</t>
+          <t>Finance lease liabilities</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Unsecured convertible notes</t>
+          <t>Loan from holding company</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Bank overdrafts</t>
+          <t>Loan from subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Unsecured bank overdrafts</t>
+          <t>Loan from associates</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Redeemable preference shares</t>
+          <t>Loan from joint venture</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Finance lease liabilities</t>
+          <t>Loan from other related companies</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Loan from holding company</t>
+          <t>Other secured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Loan from subsidiaries</t>
+          <t>Other unsecured bank facilities</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Loan from associates</t>
+          <t>Other borrowings</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Loan from joint venture</t>
-        </is>
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>*Total loans and borrowings</t>
+        </is>
+      </c>
+      <c r="B154">
+        <f>1*B138+1*B139+1*B140+1*B141+1*B144+1*B145+1*B146+1*B147+1*B148+1*B149+1*B150+1*B151+1*B152+1*B142+1*B143+1*B153</f>
+        <v/>
+      </c>
+      <c r="C154">
+        <f>1*C138+1*C139+1*C140+1*C141+1*C144+1*C145+1*C146+1*C147+1*C148+1*C149+1*C150+1*C151+1*C152+1*C142+1*C143+1*C153</f>
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Loan from other related companies</t>
+          <t>Employee benefits</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Other secured bank facilities</t>
+          <t>Cash-settled share-based payment liability</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Other unsecured bank facilities</t>
+          <t>Employment termination benefits</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Other borrowings</t>
+          <t>Provision for unconsumed leave</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>*Total loans and borrowings</t>
-        </is>
-      </c>
-      <c r="B159">
-        <f>1*B143+1*B144+1*B145+1*B146+1*B149+1*B150+1*B151+1*B152+1*B153+1*B154+1*B155+1*B156+1*B157+1*B147+1*B148+1*B158</f>
-        <v/>
-      </c>
-      <c r="C159">
-        <f>1*C143+1*C144+1*C145+1*C146+1*C149+1*C150+1*C151+1*C152+1*C153+1*C154+1*C155+1*C156+1*C157+1*C147+1*C148+1*C158</f>
-        <v/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Defined contribution plan</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Employee benefits [abstract]</t>
+          <t>Defined benefit plan</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cash-settled share-based payment liability</t>
+          <t>Other non-current employee benefits</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Employment termination benefits</t>
-        </is>
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>*Total employee benefits</t>
+        </is>
+      </c>
+      <c r="B162">
+        <f>1*B156+1*B157+1*B158+1*B159+1*B160+1*B161</f>
+        <v/>
+      </c>
+      <c r="C162">
+        <f>1*C156+1*C157+1*C158+1*C159+1*C160+1*C161</f>
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Provision for unconsumed leave</t>
+          <t>Provisions</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Defined contribution plan</t>
+          <t>Warranty provision</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Defined benefit plan</t>
+          <t>Restructuring provision</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Other non-current employee benefits</t>
+          <t>Legal proceedings provision</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
-        <is>
-          <t>*Total employee benefits</t>
-        </is>
-      </c>
-      <c r="B167">
-        <f>1*B161+1*B162+1*B163+1*B164+1*B165+1*B166</f>
-        <v/>
-      </c>
-      <c r="C167">
-        <f>1*C161+1*C162+1*C163+1*C164+1*C165+1*C166</f>
-        <v/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Onerous contracts provision</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Provisions [abstract]</t>
+          <t>Provisions for decommissioning, restoration and rehabilitation costs</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Warranty provision</t>
+          <t>Other provisions</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Restructuring provision</t>
-        </is>
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>*Total provisions</t>
+        </is>
+      </c>
+      <c r="B170">
+        <f>1*B164+1*B165+1*B166+1*B167+1*B168+1*B169</f>
+        <v/>
+      </c>
+      <c r="C170">
+        <f>1*C164+1*C165+1*C166+1*C167+1*C168+1*C169</f>
+        <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Legal proceedings provision</t>
+          <t>Trade and other payables</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Onerous contracts provision</t>
+          <t>Trade payables</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Provisions for decommissioning, restoration and rehabilitation costs</t>
+          <t>Trade payable due to contract suppliers</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Other provisions</t>
+          <t>Trade payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>*Total provisions</t>
-        </is>
-      </c>
-      <c r="B175">
-        <f>1*B169+1*B170+1*B171+1*B172+1*B173+1*B174</f>
-        <v/>
-      </c>
-      <c r="C175">
-        <f>1*C169+1*C170+1*C171+1*C172+1*C173+1*C174</f>
-        <v/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Trade payables due to subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Trade and other payables [abstract]</t>
+          <t>Trade payables due to associates</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Trade payables [abstract]</t>
+          <t>Trade payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Trade payable due to contract suppliers</t>
+          <t>Trade payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trade payables due to holding company</t>
+          <t>Other trade payables</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Trade payables due to subsidiaries</t>
-        </is>
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>*Total trade payables</t>
+        </is>
+      </c>
+      <c r="B180">
+        <f>1*B173+1*B174+1*B175+1*B176+1*B177+1*B178+1*B179</f>
+        <v/>
+      </c>
+      <c r="C180">
+        <f>1*C173+1*C174+1*C175+1*C176+1*C177+1*C178+1*C179</f>
+        <v/>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Trade payables due to associates</t>
+          <t>Other payables</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Trade payables due to joint ventures</t>
+          <t>Other payables due to related parties</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Trade payables due to other related parties</t>
+          <t>Other payables due to holding company</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Other trade payables</t>
+          <t>Other payables due to subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="inlineStr">
-        <is>
-          <t>*Total trade payables</t>
-        </is>
-      </c>
-      <c r="B185">
-        <f>1*B178+1*B179+1*B180+1*B181+1*B182+1*B183+1*B184</f>
-        <v/>
-      </c>
-      <c r="C185">
-        <f>1*C178+1*C179+1*C180+1*C181+1*C182+1*C183+1*C184</f>
-        <v/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Other payables due to associates</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Other payables [abstract]</t>
+          <t>Other payables due to joint ventures</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Other payables due to related parties [abstract]</t>
+          <t>Other payables due to other related parties</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Other payables due to holding company</t>
-        </is>
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>*Total other payables due to related parties</t>
+        </is>
+      </c>
+      <c r="B188">
+        <f>1*B183+1*B184+1*B185+1*B186+1*B187</f>
+        <v/>
+      </c>
+      <c r="C188">
+        <f>1*C183+1*C184+1*C185+1*C186+1*C187</f>
+        <v/>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Other payables due to subsidiaries</t>
+          <t>Non-trade payables</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Other payables due to associates</t>
+          <t>Deferred income</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Other payables due to joint ventures</t>
+          <t>Accruals</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Other payables due to other related parties</t>
+          <t>Retention payables</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr">
-        <is>
-          <t>*Total other payables due to related parties</t>
-        </is>
-      </c>
-      <c r="B193">
-        <f>1*B188+1*B189+1*B190+1*B191+1*B192</f>
-        <v/>
-      </c>
-      <c r="C193">
-        <f>1*C188+1*C189+1*C190+1*C191+1*C192</f>
-        <v/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Other non-trade payables</t>
+        </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Non-trade payables [abstract]</t>
-        </is>
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>*Total non-trade payables</t>
+        </is>
+      </c>
+      <c r="B194">
+        <f>1*B190+1*B191+1*B192+1*B193</f>
+        <v/>
+      </c>
+      <c r="C194">
+        <f>1*C190+1*C191+1*C192+1*C193</f>
+        <v/>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Deferred income</t>
-        </is>
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>*Total other payables</t>
+        </is>
+      </c>
+      <c r="B195">
+        <f>1*B188+1*B194</f>
+        <v/>
+      </c>
+      <c r="C195">
+        <f>1*C188+1*C194</f>
+        <v/>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Accruals</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Retention payables</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Other non-trade payables</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr">
-        <is>
-          <t>*Total non-trade payables</t>
-        </is>
-      </c>
-      <c r="B199">
-        <f>1*B195+1*B196+1*B197+1*B198</f>
-        <v/>
-      </c>
-      <c r="C199">
-        <f>1*C195+1*C196+1*C197+1*C198</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="inlineStr">
-        <is>
-          <t>*Total other payables</t>
-        </is>
-      </c>
-      <c r="B200">
-        <f>1*B193+1*B199</f>
-        <v/>
-      </c>
-      <c r="C200">
-        <f>1*C193+1*C199</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="inlineStr">
+      <c r="A196" s="1" t="inlineStr">
         <is>
           <t>*Total trade and other payables</t>
         </is>
       </c>
-      <c r="B201">
-        <f>1*B185+1*B200</f>
-        <v/>
-      </c>
-      <c r="C201">
-        <f>1*C185+1*C200</f>
+      <c r="B196">
+        <f>1*B180+1*B195</f>
+        <v/>
+      </c>
+      <c r="C196">
+        <f>1*C180+1*C195</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/02-SOFP-OrderOfLiquidity.xlsx
+++ b/XBRL-template-MPERS/Company/02-SOFP-OrderOfLiquidity.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +28,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,21 +456,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement of financial position</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
@@ -643,7 +654,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>*Total assets</t>
         </is>
@@ -658,14 +669,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Equity and liabilities</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
@@ -716,7 +727,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>*Total equity attributable to owners</t>
         </is>
@@ -753,7 +764,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>*Total equity</t>
         </is>
@@ -768,7 +779,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
@@ -863,7 +874,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>*Total liabilities</t>
         </is>
@@ -878,7 +889,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>*Total equity and liabilities</t>
         </is>
@@ -930,42 +941,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement on sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Sub-classification of assets, liabilities and equity</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Land and buildings</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
@@ -993,7 +1004,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>*Total land</t>
         </is>
@@ -1008,7 +1019,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Buildings</t>
         </is>
@@ -1043,7 +1054,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>*Total buildings</t>
         </is>
@@ -1058,7 +1069,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>*Total land and buildings</t>
         </is>
@@ -1115,7 +1126,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>*Total property, plant and equipment</t>
         </is>
@@ -1130,7 +1141,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Investment properties</t>
         </is>
@@ -1172,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>*Total investment properties</t>
         </is>
@@ -1187,14 +1198,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Intangible assets and goodwill</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Intangible assets other than goodwill</t>
         </is>
@@ -1215,7 +1226,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>*Total intangible assets other than goodwill</t>
         </is>
@@ -1237,7 +1248,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>*Total intangible assets and goodwill</t>
         </is>
@@ -1252,7 +1263,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>Investments in subsidiaries</t>
         </is>
@@ -1287,7 +1298,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>*Total investments in subsidiaries</t>
         </is>
@@ -1302,7 +1313,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Investments in associates</t>
         </is>
@@ -1344,7 +1355,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>*Total investments in associates</t>
         </is>
@@ -1359,7 +1370,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>Investments in joint ventures</t>
         </is>
@@ -1401,7 +1412,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>*Total of investments in joint ventures</t>
         </is>
@@ -1416,7 +1427,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
@@ -1458,7 +1469,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>*Total inventories</t>
         </is>
@@ -1473,14 +1484,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t>Trade and other receivables</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
@@ -1536,7 +1547,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>*Total trade receivables</t>
         </is>
@@ -1551,14 +1562,14 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
         <is>
           <t>Other receivables</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>Other receivables due from related parties</t>
         </is>
@@ -1600,7 +1611,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>*Total other receivables due from related parties</t>
         </is>
@@ -1615,7 +1626,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>Prepayments and accrued income</t>
         </is>
@@ -1636,7 +1647,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>*Total prepayments and accrued income</t>
         </is>
@@ -1651,7 +1662,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>Non-trade receivables</t>
         </is>
@@ -1693,7 +1704,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>*Total non-trade receivables</t>
         </is>
@@ -1708,7 +1719,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>*Total other receivables</t>
         </is>
@@ -1723,7 +1734,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other receivables</t>
         </is>
@@ -1738,14 +1749,14 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
@@ -1766,7 +1777,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>*Total cash</t>
         </is>
@@ -1781,7 +1792,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>Cash equivalents</t>
         </is>
@@ -1837,7 +1848,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>*Total cash equivalents</t>
         </is>
@@ -1859,7 +1870,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>*Total cash and cash equivalents</t>
         </is>
@@ -1874,7 +1885,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="1" t="inlineStr">
         <is>
           <t>Issued capital</t>
         </is>
@@ -1902,7 +1913,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>*Total issued capital</t>
         </is>
@@ -1917,14 +1928,14 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="1" t="inlineStr">
         <is>
           <t>Reserves</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>Non-distributable</t>
         </is>
@@ -1959,7 +1970,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>*Total non-distributable reserves</t>
         </is>
@@ -1974,7 +1985,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="1" t="inlineStr">
         <is>
           <t>Distributable</t>
         </is>
@@ -1988,7 +1999,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>*Total distributable reserves</t>
         </is>
@@ -2003,7 +2014,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>*Total reserves</t>
         </is>
@@ -2018,7 +2029,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="1" t="inlineStr">
         <is>
           <t>Equity - others components</t>
         </is>
@@ -2053,7 +2064,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>*Total equity - other components</t>
         </is>
@@ -2068,7 +2079,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="1" t="inlineStr">
         <is>
           <t>Loans and Borrowings</t>
         </is>
@@ -2187,7 +2198,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>*Total loans and borrowings</t>
         </is>
@@ -2202,7 +2213,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="1" t="inlineStr">
         <is>
           <t>Employee benefits</t>
         </is>
@@ -2251,7 +2262,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>*Total employee benefits</t>
         </is>
@@ -2266,7 +2277,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="1" t="inlineStr">
         <is>
           <t>Provisions</t>
         </is>
@@ -2315,7 +2326,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>*Total provisions</t>
         </is>
@@ -2330,14 +2341,14 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
         <is>
           <t>Trade and other payables</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
@@ -2393,7 +2404,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="inlineStr">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>*Total trade payables</t>
         </is>
@@ -2408,14 +2419,14 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="1" t="inlineStr">
         <is>
           <t>Other payables</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>Other payables due to related parties</t>
         </is>
@@ -2457,7 +2468,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>*Total other payables due to related parties</t>
         </is>
@@ -2472,7 +2483,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="1" t="inlineStr">
         <is>
           <t>Non-trade payables</t>
         </is>
@@ -2507,7 +2518,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>*Total non-trade payables</t>
         </is>
@@ -2522,7 +2533,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>*Total other payables</t>
         </is>
@@ -2537,7 +2548,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>*Total trade and other payables</t>
         </is>
